--- a/Device_Config_Rings.xlsx
+++ b/Device_Config_Rings.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abmai\Downloads\Aeluma_1\Aeluma_1_Ankit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB8CB8C-A385-442C-B9EC-21941B0C0444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA121769-E3D4-4045-83A4-396A771DA095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15320" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PhC_APF_EC" sheetId="65" r:id="rId1"/>
-    <sheet name="PhC_APFP_EC" sheetId="64" r:id="rId2"/>
-    <sheet name="PhC_APFP_GC" sheetId="63" r:id="rId3"/>
-    <sheet name="PhC_APF_GC" sheetId="62" r:id="rId4"/>
-    <sheet name="APFPulley_EC" sheetId="61" r:id="rId5"/>
-    <sheet name="APF_EC" sheetId="60" r:id="rId6"/>
-    <sheet name="ADF_EC" sheetId="58" r:id="rId7"/>
-    <sheet name="ECParams" sheetId="57" r:id="rId8"/>
-    <sheet name="GCParams" sheetId="56" r:id="rId9"/>
-    <sheet name="ADF_GC" sheetId="55" r:id="rId10"/>
-    <sheet name="APFPulley_GC" sheetId="54" r:id="rId11"/>
-    <sheet name="IO_GC" sheetId="51" r:id="rId12"/>
-    <sheet name="APF_GC" sheetId="50" r:id="rId13"/>
+    <sheet name="PhC_ADF_EC" sheetId="66" r:id="rId1"/>
+    <sheet name="PhC_APF_EC" sheetId="65" r:id="rId2"/>
+    <sheet name="PhC_APFP_EC" sheetId="64" r:id="rId3"/>
+    <sheet name="PhC_APFP_GC" sheetId="63" r:id="rId4"/>
+    <sheet name="PhC_APF_GC" sheetId="62" r:id="rId5"/>
+    <sheet name="APFPulley_EC" sheetId="61" r:id="rId6"/>
+    <sheet name="APF_EC" sheetId="60" r:id="rId7"/>
+    <sheet name="ADF_EC" sheetId="58" r:id="rId8"/>
+    <sheet name="ECParams" sheetId="57" r:id="rId9"/>
+    <sheet name="GCParams" sheetId="56" r:id="rId10"/>
+    <sheet name="ADF_GC" sheetId="55" r:id="rId11"/>
+    <sheet name="APFPulley_GC" sheetId="54" r:id="rId12"/>
+    <sheet name="IO_GC" sheetId="51" r:id="rId13"/>
+    <sheet name="APF_GC" sheetId="50" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="479">
   <si>
     <t>WgWidth</t>
   </si>
@@ -1286,9 +1287,6 @@
     <t>2-Quad</t>
   </si>
   <si>
-    <t>4-Bezier</t>
-  </si>
-  <si>
     <t>3-Exponetial</t>
   </si>
   <si>
@@ -1484,22 +1482,10 @@
     <t>APFP61</t>
   </si>
   <si>
-    <t>APFP62</t>
-  </si>
-  <si>
-    <t>APFP63</t>
-  </si>
-  <si>
-    <t>APFP64</t>
-  </si>
-  <si>
-    <t>APFP65</t>
-  </si>
-  <si>
-    <t>APFP66</t>
-  </si>
-  <si>
-    <t>APFP67</t>
+    <t>0.008,0.008</t>
+  </si>
+  <si>
+    <t>0.008,0.008,0.008,0.008</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1599,6 +1585,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1880,823 +1869,1099 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8818D291-C327-40A4-93BB-A1406CBD6E63}">
-  <dimension ref="A1:G35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF2BF64-98EC-416B-992F-26AC1FA7334B}">
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.1796875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.90625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="11.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="26.1796875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D2" s="1">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G2" s="11">
-        <v>200202</v>
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D2" s="9">
+        <v>20</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F2" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G2" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D3" s="1">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="9">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G3" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D4" s="9">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G4" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D5" s="9">
+        <v>20</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G5" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D6" s="9">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G6" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="9">
+        <v>20</v>
+      </c>
+      <c r="E7" s="9">
         <v>0.15</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G3" s="11">
-        <v>200203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="F7" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G7" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="9">
+        <v>20</v>
+      </c>
+      <c r="E8" s="9">
         <v>0.2</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G4" s="11">
-        <v>200204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D5" s="1">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G5" s="11">
-        <v>200205</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="F8" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G8" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="9">
+        <v>20</v>
+      </c>
+      <c r="E9" s="9">
         <v>0.3</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G6" s="11">
-        <v>200206</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D7" s="1">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="F9" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G9" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="9">
+        <v>20</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G10" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="9">
+        <v>20</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G11" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D12" s="9">
+        <v>20</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G12" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D13" s="9">
+        <v>20</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="9">
+        <v>20</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D15" s="9">
+        <v>20</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G15" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="9">
+        <v>20</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G16" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D17" s="9">
+        <v>20</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G17" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D18" s="9">
+        <v>20</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G18" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D19" s="9">
+        <v>20</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G19" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D20" s="9">
+        <v>20</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G20" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D21" s="9">
+        <v>20</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G21" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="9">
+        <v>30</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F22" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G22" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D23" s="9">
+        <v>30</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G23" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>30</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F24" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G24" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D25" s="9">
+        <v>30</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F25" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G25" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D26" s="9">
+        <v>30</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G26" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D27" s="9">
+        <v>30</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G27" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D28" s="9">
+        <v>30</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G28" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="9">
+        <v>30</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G29" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="9">
+        <v>30</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G30" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D31" s="9">
+        <v>30</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G31" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D32" s="9">
+        <v>30</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G32" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D33" s="9">
+        <v>30</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G33" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D34" s="9">
+        <v>30</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G34" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="9">
+        <v>30</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G35" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="9">
+        <v>30</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G36" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D37" s="9">
+        <v>30</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G37" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D38" s="9">
+        <v>30</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G38" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D39" s="9">
+        <v>30</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G39" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D40" s="9">
+        <v>30</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G40" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D41" s="9">
+        <v>30</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G41" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D42" s="9">
+        <v>30</v>
+      </c>
+      <c r="E42" s="9">
         <v>0.35</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G7" s="11">
-        <v>200207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D8" s="1">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G8" s="11">
-        <v>200208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D9" s="1">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G9" s="11">
-        <v>200209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D10" s="1">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G10" s="11">
-        <v>200210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G11" s="11">
-        <v>200211</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D12" s="1">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G12" s="11">
-        <v>200212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D13" s="1">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G13" s="11">
-        <v>200213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D14" s="1">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G14" s="11">
-        <v>200214</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D15" s="1">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G15" s="11">
-        <v>200215</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D16" s="1">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G16" s="11">
-        <v>200216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D17" s="1">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G17" s="11">
-        <v>200217</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D18" s="1">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G18" s="11">
-        <v>200218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D19" s="1">
-        <v>20</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G19" s="11">
-        <v>200219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D20" s="1">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G20" s="11">
-        <v>200220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D21" s="1">
-        <v>30</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G21" s="11">
-        <v>200221</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D22" s="1">
-        <v>30</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G22" s="11">
-        <v>200222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D23" s="1">
-        <v>30</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G23" s="11">
-        <v>200223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D24" s="1">
-        <v>30</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G24" s="11">
-        <v>200224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D25" s="1">
-        <v>30</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G25" s="11">
-        <v>200225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D26" s="1">
-        <v>30</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G26" s="11">
-        <v>200226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D27" s="1">
-        <v>30</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G27" s="11">
-        <v>200227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D28" s="1">
-        <v>30</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G28" s="11">
-        <v>200228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D29" s="1">
-        <v>30</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G29" s="11">
-        <v>200229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="1">
-        <v>30</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G30" s="11">
-        <v>200230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D31" s="1">
-        <v>30</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G31" s="11">
-        <v>200231</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D32" s="1">
-        <v>30</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G32" s="11">
-        <v>200232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D33" s="1">
-        <v>30</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G33" s="11">
-        <v>200233</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D34" s="1">
-        <v>30</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G34" s="11">
-        <v>200234</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D35" s="1">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G35" s="11">
-        <v>200235</v>
+      <c r="F42" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="G42" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="9">
+        <v>30</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="F43" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G43" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D44" s="9">
+        <v>30</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="F44" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="G44" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D45" s="9">
+        <v>30</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="F45" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G45" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="9">
+        <v>30</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="F46" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G46" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D47" s="9">
+        <v>30</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="F47" s="5">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="G47" s="13">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -2706,6 +2971,368 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF015CF3-8BB9-454A-A6BB-C5321D3A23AD}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="11.1796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" style="3" customWidth="1"/>
+    <col min="4" max="5" width="21.6328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.7265625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="12.08984375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.08984375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="E2" s="5">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5">
+        <v>40</v>
+      </c>
+      <c r="G2" s="5">
+        <v>25</v>
+      </c>
+      <c r="H2" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="E3" s="5">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5">
+        <v>40</v>
+      </c>
+      <c r="G3" s="5">
+        <v>25</v>
+      </c>
+      <c r="H3" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="E4" s="5">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
+        <v>40</v>
+      </c>
+      <c r="G4" s="5">
+        <v>25</v>
+      </c>
+      <c r="H4" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="E5" s="5">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
+        <v>40</v>
+      </c>
+      <c r="G5" s="5">
+        <v>25</v>
+      </c>
+      <c r="H5" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="5">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5">
+        <v>40</v>
+      </c>
+      <c r="G6" s="5">
+        <v>25</v>
+      </c>
+      <c r="H6" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="E7" s="5">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5">
+        <v>40</v>
+      </c>
+      <c r="G7" s="5">
+        <v>25</v>
+      </c>
+      <c r="H7" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="E8" s="5">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5">
+        <v>40</v>
+      </c>
+      <c r="G8" s="5">
+        <v>25</v>
+      </c>
+      <c r="H8" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="E9" s="5">
+        <v>14</v>
+      </c>
+      <c r="F9" s="5">
+        <v>40</v>
+      </c>
+      <c r="G9" s="5">
+        <v>25</v>
+      </c>
+      <c r="H9" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="E10" s="5">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5">
+        <v>40</v>
+      </c>
+      <c r="G10" s="5">
+        <v>25</v>
+      </c>
+      <c r="H10" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="E11" s="5">
+        <v>16</v>
+      </c>
+      <c r="F11" s="5">
+        <v>40</v>
+      </c>
+      <c r="G11" s="5">
+        <v>25</v>
+      </c>
+      <c r="H11" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="E12" s="5">
+        <v>17</v>
+      </c>
+      <c r="F12" s="5">
+        <v>60</v>
+      </c>
+      <c r="G12" s="5">
+        <v>25</v>
+      </c>
+      <c r="H12" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="E13" s="5">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5">
+        <v>60</v>
+      </c>
+      <c r="G13" s="5">
+        <v>25</v>
+      </c>
+      <c r="H13" s="8">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC77908D-48A1-4573-8AD2-5652F4EF691E}">
   <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4203,7 +4830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6BEABA-D1EA-40A9-A69C-BDF97CFC0D3F}">
   <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -6383,7 +7010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03D5A0A-4A9E-42CD-ACF8-25C5C28BDB4C}">
   <dimension ref="A1:J218"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -12081,7 +12708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD35A6-7677-4015-8630-AA2539733BD2}">
   <dimension ref="A1:E90"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -13631,8 +14258,1202 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8818D291-C327-40A4-93BB-A1406CBD6E63}">
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="26.1796875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D2" s="9">
+        <v>20</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F2" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G2" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="9">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G3" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D4" s="9">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G4" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D5" s="9">
+        <v>20</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G5" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D6" s="9">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G6" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="9">
+        <v>20</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G7" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="9">
+        <v>20</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G8" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="9">
+        <v>20</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G9" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="9">
+        <v>20</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G10" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="9">
+        <v>20</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G11" s="13">
+        <v>214215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D12" s="9">
+        <v>20</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G12" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D13" s="9">
+        <v>20</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="9">
+        <v>20</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D15" s="9">
+        <v>20</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G15" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="9">
+        <v>20</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G16" s="13">
+        <v>213214215216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D17" s="9">
+        <v>20</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G17" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D18" s="9">
+        <v>20</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G18" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D19" s="9">
+        <v>20</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G19" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D20" s="9">
+        <v>20</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G20" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D21" s="9">
+        <v>20</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G21" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="9">
+        <v>20</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G22" s="13">
+        <v>212213217218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D23" s="9">
+        <v>20</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>20</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G24" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D25" s="9">
+        <v>20</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G25" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D26" s="9">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F26" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G26" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D27" s="9">
+        <v>20</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G27" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D28" s="9">
+        <v>20</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G28" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="9">
+        <v>20</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="G29" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="9">
+        <v>20</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="5">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G30" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D31" s="9">
+        <v>20</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="G31" s="13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D32" s="9">
+        <v>30</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F32" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G32" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D33" s="9">
+        <v>30</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F33" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G33" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D34" s="9">
+        <v>30</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F34" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G34" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="9">
+        <v>30</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G35" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="9">
+        <v>30</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F36" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G36" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D37" s="9">
+        <v>30</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G37" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D38" s="9">
+        <v>30</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G38" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D39" s="9">
+        <v>30</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G39" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D40" s="9">
+        <v>30</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G40" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D41" s="9">
+        <v>30</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G41" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D42" s="9">
+        <v>30</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G42" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="9">
+        <v>30</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G43" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D44" s="9">
+        <v>30</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G44" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D45" s="9">
+        <v>30</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G45" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="9">
+        <v>30</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G46" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D47" s="9">
+        <v>30</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G47" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D48" s="9">
+        <v>30</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G48" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C49" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D49" s="9">
+        <v>30</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G49" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D50" s="9">
+        <v>30</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G50" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="C51" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D51" s="9">
+        <v>30</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G51" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C220B306-E2A0-4886-B112-2BB060D69FEE}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" style="6" customWidth="1"/>
@@ -13640,9 +15461,9 @@
     <col min="3" max="3" width="18.7265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.7265625" style="6" customWidth="1"/>
     <col min="5" max="6" width="15.26953125" customWidth="1"/>
-    <col min="7" max="7" width="26.1796875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.90625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="20.453125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="26.1796875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="22.6328125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="31" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
@@ -13665,14 +15486,14 @@
       <c r="F1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13695,14 +15516,14 @@
         <f>E2/D2*180/PI()</f>
         <v>17.188733853924695</v>
       </c>
-      <c r="G2" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I2" s="11">
-        <v>200202</v>
+      <c r="G2" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I2" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13722,17 +15543,17 @@
         <v>6</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F12" si="0">E3/D3*180/PI()</f>
+        <f t="shared" ref="F3:F51" si="0">E3/D3*180/PI()</f>
         <v>17.188733853924695</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I3" s="11">
-        <v>200203</v>
+      <c r="G3" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I3" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13755,14 +15576,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G4" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I4" s="11">
-        <v>200204</v>
+      <c r="G4" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I4" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13785,14 +15606,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I5" s="11">
-        <v>200205</v>
+      <c r="G5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I5" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13815,14 +15636,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I6" s="11">
-        <v>200206</v>
+      <c r="G6" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I6" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13830,7 +15651,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C7" s="1">
         <v>0.6</v>
@@ -13845,14 +15666,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G7" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I7" s="11">
-        <v>200207</v>
+      <c r="G7" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I7" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13860,7 +15681,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C8" s="1">
         <v>0.6</v>
@@ -13875,14 +15696,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="9">
         <v>0.4</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I8" s="11">
-        <v>200208</v>
+      <c r="H8" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I8" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13890,7 +15711,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="1">
         <v>0.6</v>
@@ -13905,14 +15726,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G9" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I9" s="11">
-        <v>200209</v>
+      <c r="G9" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H9" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I9" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13920,7 +15741,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C10" s="1">
         <v>0.6</v>
@@ -13935,14 +15756,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G10" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I10" s="11">
-        <v>200210</v>
+      <c r="G10" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H10" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I10" s="13">
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13950,7 +15771,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C11" s="1">
         <v>0.6</v>
@@ -13965,14 +15786,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G11" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I11" s="11">
-        <v>200211</v>
+      <c r="G11" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I11" s="13">
+        <v>214215</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13980,7 +15801,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C12" s="1">
         <v>0.6</v>
@@ -13995,14 +15816,14 @@
         <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G12" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I12" s="11">
-        <v>200212</v>
+      <c r="G12" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I12" s="13">
+        <v>214215</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14010,7 +15831,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C13" s="1">
         <v>0.6</v>
@@ -14022,17 +15843,17 @@
         <v>6</v>
       </c>
       <c r="F13" s="1">
-        <f>E13/D13*180/PI()</f>
+        <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G13" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I13" s="11">
-        <v>200213</v>
+      <c r="G13" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I13" s="13">
+        <v>214215</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14040,7 +15861,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C14" s="1">
         <v>0.6</v>
@@ -14052,17 +15873,17 @@
         <v>6</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" ref="F14:F21" si="1">E14/D14*180/PI()</f>
+        <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G14" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I14" s="11">
-        <v>200214</v>
+      <c r="G14" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I14" s="13">
+        <v>214215</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14070,7 +15891,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C15" s="1">
         <v>0.6</v>
@@ -14082,17 +15903,17 @@
         <v>6</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17.188733853924695</v>
       </c>
-      <c r="G15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I15" s="11">
-        <v>200215</v>
+      <c r="G15" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I15" s="13">
+        <v>214215</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14100,7 +15921,7 @@
         <v>69</v>
       </c>
       <c r="B16" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C16" s="1">
         <v>0.6</v>
@@ -14109,20 +15930,20 @@
         <v>20</v>
       </c>
       <c r="E16" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I16" s="11">
-        <v>200216</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H16" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I16" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14130,7 +15951,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C17" s="1">
         <v>0.6</v>
@@ -14139,20 +15960,20 @@
         <v>20</v>
       </c>
       <c r="E17" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G17" s="1">
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G17" s="9">
         <v>0.4</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I17" s="11">
-        <v>200217</v>
+      <c r="H17" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14160,7 +15981,7 @@
         <v>71</v>
       </c>
       <c r="B18" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C18" s="1">
         <v>0.6</v>
@@ -14169,20 +15990,20 @@
         <v>20</v>
       </c>
       <c r="E18" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I18" s="11">
-        <v>200218</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I18" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14190,7 +16011,7 @@
         <v>72</v>
       </c>
       <c r="B19" s="1">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C19" s="1">
         <v>0.6</v>
@@ -14199,20 +16020,20 @@
         <v>20</v>
       </c>
       <c r="E19" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I19" s="11">
-        <v>200219</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I19" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14220,7 +16041,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C20" s="1">
         <v>0.6</v>
@@ -14229,20 +16050,20 @@
         <v>20</v>
       </c>
       <c r="E20" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I20" s="11">
-        <v>200220</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I20" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14250,7 +16071,7 @@
         <v>74</v>
       </c>
       <c r="B21" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C21" s="1">
         <v>0.6</v>
@@ -14259,20 +16080,20 @@
         <v>20</v>
       </c>
       <c r="E21" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I21" s="11">
-        <v>200221</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I21" s="13">
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14280,7 +16101,7 @@
         <v>75</v>
       </c>
       <c r="B22" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C22" s="1">
         <v>0.6</v>
@@ -14289,20 +16110,20 @@
         <v>20</v>
       </c>
       <c r="E22" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" ref="F22:F29" si="2">E22/D22*180/PI()</f>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I22" s="11">
-        <v>200222</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I22" s="13">
+        <v>213214215216</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14310,7 +16131,7 @@
         <v>76</v>
       </c>
       <c r="B23" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C23" s="1">
         <v>0.6</v>
@@ -14319,20 +16140,20 @@
         <v>20</v>
       </c>
       <c r="E23" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I23" s="11">
-        <v>200223</v>
+        <f t="shared" si="0"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I23" s="13">
+        <v>213214215216</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14340,7 +16161,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C24" s="1">
         <v>0.6</v>
@@ -14349,20 +16170,20 @@
         <v>20</v>
       </c>
       <c r="E24" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I24" s="11">
-        <v>200224</v>
+        <f t="shared" ref="F24:F31" si="1">E24/D24*180/PI()</f>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I24" s="13">
+        <v>213214215216</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14370,29 +16191,29 @@
         <v>78</v>
       </c>
       <c r="B25" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="1">
         <v>0.6</v>
       </c>
       <c r="D25" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I25" s="11">
-        <v>200225</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I25" s="13">
+        <v>213214215216</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14400,29 +16221,29 @@
         <v>79</v>
       </c>
       <c r="B26" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="1">
         <v>0.6</v>
       </c>
       <c r="D26" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I26" s="11">
-        <v>200226</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I26" s="13">
+        <v>213214215216</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14430,29 +16251,29 @@
         <v>80</v>
       </c>
       <c r="B27" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C27" s="1">
         <v>0.6</v>
       </c>
       <c r="D27" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I27" s="11">
-        <v>200227</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I27" s="13">
+        <v>212213217218</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14460,29 +16281,29 @@
         <v>81</v>
       </c>
       <c r="B28" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C28" s="1">
         <v>0.6</v>
       </c>
       <c r="D28" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I28" s="11">
-        <v>200228</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I28" s="13">
+        <v>212213217218</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14490,29 +16311,29 @@
         <v>82</v>
       </c>
       <c r="B29" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C29" s="1">
         <v>0.6</v>
       </c>
       <c r="D29" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F29" s="1">
-        <f t="shared" si="2"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I29" s="11">
-        <v>200229</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I29" s="13">
+        <v>212213217218</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14526,23 +16347,23 @@
         <v>0.6</v>
       </c>
       <c r="D30" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" ref="F30:F32" si="3">E30/D30*180/PI()</f>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I30" s="11">
-        <v>200230</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I30" s="13">
+        <v>212213217218</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14556,23 +16377,23 @@
         <v>0.6</v>
       </c>
       <c r="D31" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F31" s="1">
-        <f t="shared" si="3"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I31" s="11">
-        <v>200231</v>
+        <f t="shared" si="1"/>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I31" s="13">
+        <v>212213217218</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14580,7 +16401,7 @@
         <v>85</v>
       </c>
       <c r="B32" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C32" s="1">
         <v>0.6</v>
@@ -14589,20 +16410,590 @@
         <v>30</v>
       </c>
       <c r="E32" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1">
-        <f t="shared" si="3"/>
-        <v>22.918311805232928</v>
-      </c>
-      <c r="G32" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I32" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D33" s="1">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I33" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D34" s="1">
+        <v>30</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I34" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="1">
+        <v>30</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I35" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="1">
+        <v>30</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I36" s="13">
+        <v>320321322323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D37" s="1">
+        <v>30</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I37" s="13">
+        <v>319320324325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D38" s="1">
+        <v>30</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G38" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I38" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D39" s="1">
+        <v>30</v>
+      </c>
+      <c r="E39" s="1">
+        <v>8</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G39" s="5">
         <v>0.3</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="I32" s="11">
-        <v>200232</v>
+      <c r="H39" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I39" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D40" s="1">
+        <v>30</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H40" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I40" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D41" s="1">
+        <v>30</v>
+      </c>
+      <c r="E41" s="1">
+        <v>8</v>
+      </c>
+      <c r="F41" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I41" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D42" s="1">
+        <v>30</v>
+      </c>
+      <c r="E42" s="1">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G42" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H42" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I42" s="13">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="1">
+        <v>30</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I43" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D44" s="1">
+        <v>30</v>
+      </c>
+      <c r="E44" s="1">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G44" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I44" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D45" s="1">
+        <v>30</v>
+      </c>
+      <c r="E45" s="1">
+        <v>8</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I45" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="1">
+        <v>30</v>
+      </c>
+      <c r="E46" s="1">
+        <v>8</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G46" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I46" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D47" s="1">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G47" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I47" s="13">
+        <v>321322</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D48" s="1">
+        <v>30</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G48" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I48" s="13">
+        <v>321322323324</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D49" s="1">
+        <v>30</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8</v>
+      </c>
+      <c r="F49" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G49" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I49" s="13">
+        <v>321322323324</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D50" s="1">
+        <v>30</v>
+      </c>
+      <c r="E50" s="1">
+        <v>8</v>
+      </c>
+      <c r="F50" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G50" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I50" s="13">
+        <v>321322323324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D51" s="1">
+        <v>30</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8</v>
+      </c>
+      <c r="F51" s="1">
+        <f t="shared" si="0"/>
+        <v>15.278874536821952</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I51" s="13">
+        <v>321322323324</v>
       </c>
     </row>
   </sheetData>
@@ -14611,7 +17002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35679A9-667F-4990-AB3E-8B01407FE0F5}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14650,10 +17041,10 @@
         <v>1</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14680,7 +17071,7 @@
         <v>0.1</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I2" s="11">
         <v>200202</v>
@@ -14710,7 +17101,7 @@
         <v>0.1</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I3" s="11">
         <v>200202</v>
@@ -14740,7 +17131,7 @@
         <v>0.1</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I4" s="11">
         <v>200202</v>
@@ -14770,7 +17161,7 @@
         <v>0.1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I5" s="11">
         <v>200202</v>
@@ -14800,7 +17191,7 @@
         <v>0.1</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I6" s="11">
         <v>200202</v>
@@ -14830,7 +17221,7 @@
         <v>0.1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I7" s="11">
         <v>200202</v>
@@ -14860,7 +17251,7 @@
         <v>0.1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I8" s="11">
         <v>200202</v>
@@ -14890,7 +17281,7 @@
         <v>0.1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I9" s="11">
         <v>200202</v>
@@ -14920,7 +17311,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I10" s="11">
         <v>200202</v>
@@ -14950,7 +17341,7 @@
         <v>0.1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I11" s="11">
         <v>200202</v>
@@ -14980,7 +17371,7 @@
         <v>0.1</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I12" s="11">
         <v>200202</v>
@@ -15010,7 +17401,7 @@
         <v>0.1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I13" s="11">
         <v>200202</v>
@@ -15040,7 +17431,7 @@
         <v>0.1</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I14" s="11">
         <v>200202</v>
@@ -15070,7 +17461,7 @@
         <v>0.1</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I15" s="11">
         <v>200202</v>
@@ -15100,7 +17491,7 @@
         <v>0.1</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I16" s="11">
         <v>200202</v>
@@ -15130,7 +17521,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I17" s="11">
         <v>200202</v>
@@ -15160,7 +17551,7 @@
         <v>0.1</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I18" s="11">
         <v>200202</v>
@@ -15190,7 +17581,7 @@
         <v>0.1</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I19" s="11">
         <v>200202</v>
@@ -15220,7 +17611,7 @@
         <v>0.1</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I20" s="11">
         <v>200202</v>
@@ -15250,7 +17641,7 @@
         <v>0.1</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I21" s="11">
         <v>200202</v>
@@ -15280,7 +17671,7 @@
         <v>0.1</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I22" s="11">
         <v>200202</v>
@@ -15310,7 +17701,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I23" s="11">
         <v>200202</v>
@@ -15340,7 +17731,7 @@
         <v>0.1</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I24" s="11">
         <v>200202</v>
@@ -15370,7 +17761,7 @@
         <v>0.1</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I25" s="11">
         <v>200202</v>
@@ -15400,7 +17791,7 @@
         <v>0.1</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I26" s="11">
         <v>200202</v>
@@ -15430,7 +17821,7 @@
         <v>0.1</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I27" s="11">
         <v>200202</v>
@@ -15460,7 +17851,7 @@
         <v>0.1</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I28" s="11">
         <v>200202</v>
@@ -15490,7 +17881,7 @@
         <v>0.1</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I29" s="11">
         <v>200202</v>
@@ -15520,7 +17911,7 @@
         <v>0.1</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I30" s="11">
         <v>200202</v>
@@ -15550,7 +17941,7 @@
         <v>0.1</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I31" s="11">
         <v>200202</v>
@@ -15580,7 +17971,7 @@
         <v>0.1</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I32" s="11">
         <v>200202</v>
@@ -15610,7 +18001,7 @@
         <v>0.1</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I33" s="11">
         <v>200202</v>
@@ -15640,7 +18031,7 @@
         <v>0.1</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I34" s="11">
         <v>200202</v>
@@ -15670,7 +18061,7 @@
         <v>0.1</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I35" s="11">
         <v>200202</v>
@@ -15700,7 +18091,7 @@
         <v>0.1</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I36" s="11">
         <v>200202</v>
@@ -15730,7 +18121,7 @@
         <v>0.1</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I37" s="11">
         <v>200202</v>
@@ -15760,7 +18151,7 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I38" s="11">
         <v>200202</v>
@@ -15790,7 +18181,7 @@
         <v>0.1</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I39" s="11">
         <v>200202</v>
@@ -15820,7 +18211,7 @@
         <v>0.1</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I40" s="11">
         <v>200202</v>
@@ -15850,7 +18241,7 @@
         <v>0.1</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I41" s="11">
         <v>200202</v>
@@ -15880,7 +18271,7 @@
         <v>0.1</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I42" s="11">
         <v>200202</v>
@@ -15910,7 +18301,7 @@
         <v>0.1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I43" s="11">
         <v>200202</v>
@@ -15940,7 +18331,7 @@
         <v>0.1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I44" s="11">
         <v>200202</v>
@@ -15970,7 +18361,7 @@
         <v>0.1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I45" s="11">
         <v>200202</v>
@@ -16000,7 +18391,7 @@
         <v>0.1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I46" s="11">
         <v>200202</v>
@@ -16030,7 +18421,7 @@
         <v>0.1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I47" s="11">
         <v>200202</v>
@@ -16060,7 +18451,7 @@
         <v>0.1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I48" s="11">
         <v>200202</v>
@@ -16090,7 +18481,7 @@
         <v>0.1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I49" s="11">
         <v>200202</v>
@@ -16120,7 +18511,7 @@
         <v>0.1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I50" s="11">
         <v>200202</v>
@@ -16150,7 +18541,7 @@
         <v>0.1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I51" s="11">
         <v>200202</v>
@@ -16162,7 +18553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401744FE-A900-4F37-9AC4-D2E9881977A1}">
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -16194,10 +18585,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -16217,7 +18608,7 @@
         <v>0.1</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G2" s="11">
         <v>200202</v>
@@ -16240,7 +18631,7 @@
         <v>0.1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G3" s="11">
         <v>200202</v>
@@ -16263,7 +18654,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G4" s="11">
         <v>200202</v>
@@ -16286,7 +18677,7 @@
         <v>0.1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G5" s="11">
         <v>200202</v>
@@ -16309,7 +18700,7 @@
         <v>0.1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G6" s="11">
         <v>200202</v>
@@ -16332,7 +18723,7 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G7" s="11">
         <v>200202</v>
@@ -16355,7 +18746,7 @@
         <v>0.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G8" s="11">
         <v>200202</v>
@@ -16378,7 +18769,7 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G9" s="11">
         <v>200202</v>
@@ -16401,7 +18792,7 @@
         <v>0.1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G10" s="11">
         <v>200202</v>
@@ -16424,7 +18815,7 @@
         <v>0.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G11" s="11">
         <v>200202</v>
@@ -16447,7 +18838,7 @@
         <v>0.1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G12" s="11">
         <v>200202</v>
@@ -16470,7 +18861,7 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G13" s="11">
         <v>200202</v>
@@ -16493,7 +18884,7 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G14" s="11">
         <v>200202</v>
@@ -16516,7 +18907,7 @@
         <v>0.1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G15" s="11">
         <v>200202</v>
@@ -16539,7 +18930,7 @@
         <v>0.1</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G16" s="11">
         <v>200202</v>
@@ -16562,7 +18953,7 @@
         <v>0.1</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G17" s="11">
         <v>200202</v>
@@ -16585,7 +18976,7 @@
         <v>0.1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G18" s="11">
         <v>200202</v>
@@ -16608,7 +18999,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G19" s="11">
         <v>200202</v>
@@ -16631,7 +19022,7 @@
         <v>0.1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G20" s="11">
         <v>200202</v>
@@ -16654,7 +19045,7 @@
         <v>0.1</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G21" s="11">
         <v>200202</v>
@@ -16677,7 +19068,7 @@
         <v>0.1</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G22" s="11">
         <v>200202</v>
@@ -16700,7 +19091,7 @@
         <v>0.1</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G23" s="11">
         <v>200202</v>
@@ -16723,7 +19114,7 @@
         <v>0.1</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G24" s="11">
         <v>200202</v>
@@ -16746,7 +19137,7 @@
         <v>0.1</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G25" s="11">
         <v>200202</v>
@@ -16769,7 +19160,7 @@
         <v>0.1</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G26" s="11">
         <v>200202</v>
@@ -16792,7 +19183,7 @@
         <v>0.1</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G27" s="11">
         <v>200202</v>
@@ -16815,7 +19206,7 @@
         <v>0.1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G28" s="11">
         <v>200202</v>
@@ -16838,7 +19229,7 @@
         <v>0.1</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G29" s="11">
         <v>200202</v>
@@ -16861,7 +19252,7 @@
         <v>0.1</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G30" s="11">
         <v>200202</v>
@@ -16884,7 +19275,7 @@
         <v>0.1</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G31" s="11">
         <v>200202</v>
@@ -16907,7 +19298,7 @@
         <v>0.1</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G32" s="11">
         <v>200202</v>
@@ -16930,7 +19321,7 @@
         <v>0.1</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G33" s="11">
         <v>200202</v>
@@ -16953,7 +19344,7 @@
         <v>0.1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G34" s="11">
         <v>200202</v>
@@ -16976,7 +19367,7 @@
         <v>0.1</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G35" s="11">
         <v>200202</v>
@@ -16999,7 +19390,7 @@
         <v>0.1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G36" s="11">
         <v>200202</v>
@@ -17022,7 +19413,7 @@
         <v>0.1</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G37" s="11">
         <v>200202</v>
@@ -17045,7 +19436,7 @@
         <v>0.1</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G38" s="11">
         <v>200202</v>
@@ -17068,7 +19459,7 @@
         <v>0.1</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G39" s="11">
         <v>200202</v>
@@ -17091,7 +19482,7 @@
         <v>0.1</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G40" s="11">
         <v>200202</v>
@@ -17114,7 +19505,7 @@
         <v>0.1</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G41" s="11">
         <v>200202</v>
@@ -17137,7 +19528,7 @@
         <v>0.1</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G42" s="11">
         <v>200202</v>
@@ -17160,7 +19551,7 @@
         <v>0.1</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G43" s="11">
         <v>200202</v>
@@ -17183,7 +19574,7 @@
         <v>0.1</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G44" s="11">
         <v>200202</v>
@@ -17206,7 +19597,7 @@
         <v>0.1</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G45" s="11">
         <v>200202</v>
@@ -17229,7 +19620,7 @@
         <v>0.1</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G46" s="11">
         <v>200202</v>
@@ -17252,7 +19643,7 @@
         <v>0.1</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G47" s="11">
         <v>200202</v>
@@ -17275,7 +19666,7 @@
         <v>0.1</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G48" s="11">
         <v>200202</v>
@@ -17298,7 +19689,7 @@
         <v>0.1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G49" s="11">
         <v>200202</v>
@@ -17321,7 +19712,7 @@
         <v>0.1</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G50" s="11">
         <v>200202</v>
@@ -17344,7 +19735,7 @@
         <v>0.1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G51" s="11">
         <v>200202</v>
@@ -17356,9 +19747,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC47C97-1CBF-4053-ADE7-65D175B80652}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" style="6" customWidth="1"/>
@@ -17395,7 +19786,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B2" s="9">
         <v>0.6</v>
@@ -17407,11 +19798,11 @@
         <v>15</v>
       </c>
       <c r="E2" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="9">
         <f>E2/D2*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G2" s="9">
         <v>0.15</v>
@@ -17419,7 +19810,7 @@
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B3" s="9">
         <v>0.6</v>
@@ -17431,11 +19822,11 @@
         <v>15</v>
       </c>
       <c r="E3" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="9">
         <f t="shared" ref="F3:F12" si="0">E3/D3*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G3" s="9">
         <v>0.2</v>
@@ -17443,7 +19834,7 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B4" s="9">
         <v>0.6</v>
@@ -17455,11 +19846,11 @@
         <v>15</v>
       </c>
       <c r="E4" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G4" s="9">
         <v>0.25</v>
@@ -17467,7 +19858,7 @@
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B5" s="9">
         <v>0.6</v>
@@ -17479,11 +19870,11 @@
         <v>15</v>
       </c>
       <c r="E5" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G5" s="9">
         <v>0.3</v>
@@ -17491,7 +19882,7 @@
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B6" s="9">
         <v>0.6</v>
@@ -17503,11 +19894,11 @@
         <v>15</v>
       </c>
       <c r="E6" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G6" s="9">
         <v>0.35</v>
@@ -17515,7 +19906,7 @@
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B7" s="9">
         <v>0.6</v>
@@ -17527,11 +19918,11 @@
         <v>15</v>
       </c>
       <c r="E7" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G7" s="9">
         <v>0.4</v>
@@ -17539,7 +19930,7 @@
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B8" s="9">
         <v>0.6</v>
@@ -17551,11 +19942,11 @@
         <v>15</v>
       </c>
       <c r="E8" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G8" s="9">
         <v>0.45</v>
@@ -17563,7 +19954,7 @@
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B9" s="9">
         <v>0.6</v>
@@ -17575,11 +19966,11 @@
         <v>15</v>
       </c>
       <c r="E9" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G9" s="9">
         <v>0.5</v>
@@ -17587,7 +19978,7 @@
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B10" s="9">
         <v>0.7</v>
@@ -17599,11 +19990,11 @@
         <v>15</v>
       </c>
       <c r="E10" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G10" s="9">
         <v>0.2</v>
@@ -17611,7 +20002,7 @@
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B11" s="9">
         <v>0.7</v>
@@ -17623,11 +20014,11 @@
         <v>15</v>
       </c>
       <c r="E11" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G11" s="9">
         <v>0.4</v>
@@ -17635,7 +20026,7 @@
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B12" s="9">
         <v>0.7</v>
@@ -17647,11 +20038,11 @@
         <v>15</v>
       </c>
       <c r="E12" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="9">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G12" s="9">
         <v>0.5</v>
@@ -17659,10 +20050,10 @@
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B13" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="9">
         <v>0.6</v>
@@ -17671,19 +20062,19 @@
         <v>15</v>
       </c>
       <c r="E13" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="9">
-        <f>E13/D13*180/PI()</f>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F13:F44" si="1">E13/D13*180/PI()</f>
+        <v>15.278874536821952</v>
       </c>
       <c r="G13" s="9">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B14" s="9">
         <v>0.8</v>
@@ -17695,19 +20086,19 @@
         <v>15</v>
       </c>
       <c r="E14" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="9">
-        <f t="shared" ref="F14:F49" si="1">E14/D14*180/PI()</f>
-        <v>22.918311805232928</v>
+        <f t="shared" si="1"/>
+        <v>15.278874536821952</v>
       </c>
       <c r="G14" s="9">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B15" s="9">
         <v>0.8</v>
@@ -17719,19 +20110,19 @@
         <v>15</v>
       </c>
       <c r="E15" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G15" s="9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B16" s="9">
         <v>0.8</v>
@@ -17743,67 +20134,67 @@
         <v>15</v>
       </c>
       <c r="E16" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G16" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B17" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C17" s="9">
         <v>0.6</v>
       </c>
       <c r="D17" s="9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E17" s="9">
         <v>6</v>
       </c>
       <c r="F17" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G17" s="9">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B18" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C18" s="9">
         <v>0.6</v>
       </c>
       <c r="D18" s="9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="9">
         <v>6</v>
       </c>
       <c r="F18" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G18" s="9">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B19" s="9">
         <v>0.6</v>
@@ -17815,19 +20206,19 @@
         <v>20</v>
       </c>
       <c r="E19" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G19" s="9">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B20" s="9">
         <v>0.6</v>
@@ -17839,19 +20230,19 @@
         <v>20</v>
       </c>
       <c r="E20" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G20" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B21" s="9">
         <v>0.6</v>
@@ -17863,19 +20254,19 @@
         <v>20</v>
       </c>
       <c r="E21" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G21" s="9">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B22" s="9">
         <v>0.6</v>
@@ -17887,19 +20278,19 @@
         <v>20</v>
       </c>
       <c r="E22" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G22" s="9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B23" s="9">
         <v>0.6</v>
@@ -17911,19 +20302,19 @@
         <v>20</v>
       </c>
       <c r="E23" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G23" s="9">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B24" s="9">
         <v>0.6</v>
@@ -17935,19 +20326,19 @@
         <v>20</v>
       </c>
       <c r="E24" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G24" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B25" s="9">
         <v>0.6</v>
@@ -17959,19 +20350,19 @@
         <v>20</v>
       </c>
       <c r="E25" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G25" s="9">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B26" s="9">
         <v>0.6</v>
@@ -17983,22 +20374,22 @@
         <v>20</v>
       </c>
       <c r="E26" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G26" s="9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B27" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="9">
         <v>0.6</v>
@@ -18007,22 +20398,22 @@
         <v>20</v>
       </c>
       <c r="E27" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G27" s="9">
-        <v>0.55000000000000004</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B28" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C28" s="9">
         <v>0.6</v>
@@ -18031,22 +20422,22 @@
         <v>20</v>
       </c>
       <c r="E28" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G28" s="9">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B29" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C29" s="9">
         <v>0.6</v>
@@ -18055,22 +20446,22 @@
         <v>20</v>
       </c>
       <c r="E29" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G29" s="9">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B30" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C30" s="9">
         <v>0.6</v>
@@ -18079,19 +20470,19 @@
         <v>20</v>
       </c>
       <c r="E30" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G30" s="9">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B31" s="9">
         <v>0.7</v>
@@ -18103,19 +20494,19 @@
         <v>20</v>
       </c>
       <c r="E31" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G31" s="9">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B32" s="9">
         <v>0.7</v>
@@ -18127,22 +20518,22 @@
         <v>20</v>
       </c>
       <c r="E32" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
+        <v>17.188733853924695</v>
       </c>
       <c r="G32" s="9">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B33" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C33" s="9">
         <v>0.6</v>
@@ -18151,22 +20542,22 @@
         <v>20</v>
       </c>
       <c r="E33" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
-      </c>
-      <c r="G33" s="9">
-        <v>0.45</v>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B34" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C34" s="9">
         <v>0.6</v>
@@ -18175,22 +20566,22 @@
         <v>20</v>
       </c>
       <c r="E34" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
-      </c>
-      <c r="G34" s="9">
-        <v>0.55000000000000004</v>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0.35</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B35" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C35" s="9">
         <v>0.6</v>
@@ -18199,22 +20590,22 @@
         <v>20</v>
       </c>
       <c r="E35" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
-      </c>
-      <c r="G35" s="9">
-        <v>0.65</v>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0.45</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B36" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C36" s="9">
         <v>0.6</v>
@@ -18223,35 +20614,35 @@
         <v>20</v>
       </c>
       <c r="E36" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F36" s="9">
         <f t="shared" si="1"/>
-        <v>25.783100780887047</v>
-      </c>
-      <c r="G36" s="9">
-        <v>0.75</v>
+        <v>17.188733853924695</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B37" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C37" s="9">
         <v>0.6</v>
       </c>
       <c r="D37" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E37" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F37" s="9">
         <f t="shared" si="1"/>
-        <v>34.377467707849391</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G37" s="5">
         <v>0.25</v>
@@ -18259,103 +20650,103 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B38" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C38" s="9">
         <v>0.6</v>
       </c>
       <c r="D38" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E38" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F38" s="9">
         <f t="shared" si="1"/>
-        <v>34.377467707849391</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G38" s="5">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B39" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C39" s="9">
         <v>0.6</v>
       </c>
       <c r="D39" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E39" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="9">
         <f t="shared" si="1"/>
-        <v>34.377467707849391</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G39" s="5">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B40" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C40" s="9">
         <v>0.6</v>
       </c>
       <c r="D40" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E40" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F40" s="9">
         <f t="shared" si="1"/>
-        <v>34.377467707849391</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G40" s="5">
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B41" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C41" s="9">
         <v>0.6</v>
       </c>
       <c r="D41" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E41" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F41" s="9">
         <f t="shared" si="1"/>
-        <v>34.377467707849391</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G41" s="5">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B42" s="9">
         <v>0.6</v>
@@ -18367,22 +20758,22 @@
         <v>30</v>
       </c>
       <c r="E42" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F42" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G42" s="5">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B43" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C43" s="9">
         <v>0.6</v>
@@ -18391,22 +20782,22 @@
         <v>30</v>
       </c>
       <c r="E43" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F43" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G43" s="5">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B44" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C44" s="9">
         <v>0.6</v>
@@ -18415,22 +20806,22 @@
         <v>30</v>
       </c>
       <c r="E44" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F44" s="9">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G44" s="5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B45" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C45" s="9">
         <v>0.6</v>
@@ -18439,22 +20830,22 @@
         <v>30</v>
       </c>
       <c r="E45" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F45" s="9">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F45" si="2">E45/D45*180/PI()</f>
+        <v>15.278874536821952</v>
       </c>
       <c r="G45" s="5">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B46" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C46" s="9">
         <v>0.6</v>
@@ -18463,22 +20854,22 @@
         <v>30</v>
       </c>
       <c r="E46" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F46" s="9">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F46" si="3">E46/D46*180/PI()</f>
+        <v>15.278874536821952</v>
       </c>
       <c r="G46" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B47" s="9">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C47" s="9">
         <v>0.6</v>
@@ -18487,22 +20878,22 @@
         <v>30</v>
       </c>
       <c r="E47" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F47" s="9">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F47:F48" si="4">E47/D47*180/PI()</f>
+        <v>15.278874536821952</v>
       </c>
       <c r="G47" s="5">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B48" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C48" s="9">
         <v>0.6</v>
@@ -18511,190 +20902,190 @@
         <v>30</v>
       </c>
       <c r="E48" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F48" s="9">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <f t="shared" si="4"/>
+        <v>15.278874536821952</v>
       </c>
       <c r="G48" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B49" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="C49" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="C49" s="5">
         <v>0.6</v>
       </c>
       <c r="D49" s="9">
         <v>30</v>
       </c>
       <c r="E49" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F49" s="9">
-        <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F49:F51" si="5">E49/D49*180/PI()</f>
+        <v>15.278874536821952</v>
       </c>
       <c r="G49" s="5">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B50" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="C50" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="C50" s="5">
         <v>0.6</v>
       </c>
       <c r="D50" s="9">
         <v>30</v>
       </c>
       <c r="E50" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F50" s="9">
-        <f t="shared" ref="F50" si="2">E50/D50*180/PI()</f>
-        <v>22.918311805232928</v>
+        <f t="shared" si="5"/>
+        <v>15.278874536821952</v>
       </c>
       <c r="G50" s="5">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="B51" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="C51" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D51" s="9">
-        <v>30</v>
+        <v>465</v>
+      </c>
+      <c r="B51" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D51" s="5">
+        <v>40</v>
       </c>
       <c r="E51" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F51" s="9">
-        <f t="shared" ref="F51" si="3">E51/D51*180/PI()</f>
-        <v>22.918311805232928</v>
+        <f t="shared" si="5"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G51" s="5">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="B52" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C52" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D52" s="9">
-        <v>30</v>
+        <v>466</v>
+      </c>
+      <c r="B52" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D52" s="5">
+        <v>40</v>
       </c>
       <c r="E52" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F52" s="9">
-        <f t="shared" ref="F52:F53" si="4">E52/D52*180/PI()</f>
-        <v>22.918311805232928</v>
+        <f t="shared" ref="F52:F62" si="6">E52/D52*180/PI()</f>
+        <v>11.459155902616464</v>
       </c>
       <c r="G52" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="B53" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C53" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D53" s="9">
-        <v>30</v>
+        <v>467</v>
+      </c>
+      <c r="B53" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D53" s="5">
+        <v>40</v>
       </c>
       <c r="E53" s="9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F53" s="9">
-        <f t="shared" si="4"/>
-        <v>22.918311805232928</v>
+        <f t="shared" si="6"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G53" s="5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="B54" s="9">
-        <v>0.8</v>
+        <v>468</v>
+      </c>
+      <c r="B54" s="5">
+        <v>0.6</v>
       </c>
       <c r="C54" s="5">
         <v>0.6</v>
       </c>
-      <c r="D54" s="9">
-        <v>30</v>
+      <c r="D54" s="5">
+        <v>40</v>
       </c>
       <c r="E54" s="9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F54" s="9">
-        <f t="shared" ref="F54:F56" si="5">E54/D54*180/PI()</f>
-        <v>26.738030439438418</v>
+        <f t="shared" si="6"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G54" s="5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B55" s="9">
-        <v>0.8</v>
+        <v>469</v>
+      </c>
+      <c r="B55" s="5">
+        <v>0.7</v>
       </c>
       <c r="C55" s="5">
         <v>0.6</v>
       </c>
-      <c r="D55" s="9">
-        <v>30</v>
+      <c r="D55" s="5">
+        <v>40</v>
       </c>
       <c r="E55" s="9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F55" s="9">
-        <f t="shared" si="5"/>
-        <v>26.738030439438418</v>
+        <f t="shared" si="6"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G55" s="5">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B56" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C56" s="5">
         <v>0.6</v>
@@ -18703,22 +21094,22 @@
         <v>40</v>
       </c>
       <c r="E56" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F56" s="9">
-        <f t="shared" si="5"/>
-        <v>21.485917317405871</v>
+        <f t="shared" si="6"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G56" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B57" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C57" s="5">
         <v>0.6</v>
@@ -18727,22 +21118,22 @@
         <v>40</v>
       </c>
       <c r="E57" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F57" s="9">
-        <f t="shared" ref="F57:F68" si="6">E57/D57*180/PI()</f>
-        <v>21.485917317405871</v>
+        <f t="shared" si="6"/>
+        <v>11.459155902616464</v>
       </c>
       <c r="G57" s="5">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B58" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C58" s="5">
         <v>0.6</v>
@@ -18751,11 +21142,11 @@
         <v>40</v>
       </c>
       <c r="E58" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F58" s="9">
         <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
+        <v>11.459155902616464</v>
       </c>
       <c r="G58" s="5">
         <v>0.4</v>
@@ -18763,10 +21154,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B59" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C59" s="5">
         <v>0.6</v>
@@ -18775,22 +21166,22 @@
         <v>40</v>
       </c>
       <c r="E59" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F59" s="9">
         <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
+        <v>11.459155902616464</v>
       </c>
       <c r="G59" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B60" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C60" s="5">
         <v>0.6</v>
@@ -18799,11 +21190,11 @@
         <v>40</v>
       </c>
       <c r="E60" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F60" s="9">
         <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
+        <v>11.459155902616464</v>
       </c>
       <c r="G60" s="5">
         <v>0.2</v>
@@ -18811,10 +21202,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B61" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C61" s="5">
         <v>0.6</v>
@@ -18823,22 +21214,22 @@
         <v>40</v>
       </c>
       <c r="E61" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F61" s="9">
         <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
+        <v>11.459155902616464</v>
       </c>
       <c r="G61" s="5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B62" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C62" s="5">
         <v>0.6</v>
@@ -18847,158 +21238,14 @@
         <v>40</v>
       </c>
       <c r="E62" s="9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F62" s="9">
         <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
+        <v>11.459155902616464</v>
       </c>
       <c r="G62" s="5">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="B63" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="C63" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D63" s="5">
-        <v>40</v>
-      </c>
-      <c r="E63" s="9">
-        <v>15</v>
-      </c>
-      <c r="F63" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G63" s="5">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="B64" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="C64" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D64" s="5">
-        <v>40</v>
-      </c>
-      <c r="E64" s="9">
-        <v>15</v>
-      </c>
-      <c r="F64" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G64" s="5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="B65" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C65" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D65" s="5">
-        <v>40</v>
-      </c>
-      <c r="E65" s="9">
-        <v>15</v>
-      </c>
-      <c r="F65" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G65" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="B66" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C66" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D66" s="5">
-        <v>40</v>
-      </c>
-      <c r="E66" s="9">
-        <v>15</v>
-      </c>
-      <c r="F66" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G66" s="5">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="B67" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C67" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D67" s="5">
-        <v>40</v>
-      </c>
-      <c r="E67" s="9">
-        <v>15</v>
-      </c>
-      <c r="F67" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G67" s="5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="B68" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C68" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D68" s="5">
-        <v>40</v>
-      </c>
-      <c r="E68" s="9">
-        <v>15</v>
-      </c>
-      <c r="F68" s="9">
-        <f t="shared" si="6"/>
-        <v>21.485917317405871</v>
-      </c>
-      <c r="G68" s="5">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -19007,9 +21254,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF53911-60A1-4893-8A5A-82654856C994}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" style="6" customWidth="1"/>
@@ -19246,7 +21493,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C14" s="9">
         <v>0.6</v>
@@ -19255,7 +21502,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="9">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19272,7 +21519,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="9">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19289,7 +21536,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19306,7 +21553,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19314,16 +21561,16 @@
         <v>71</v>
       </c>
       <c r="B18" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C18" s="9">
         <v>0.6</v>
       </c>
       <c r="D18" s="9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="9">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19331,16 +21578,16 @@
         <v>72</v>
       </c>
       <c r="B19" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C19" s="9">
         <v>0.6</v>
       </c>
       <c r="D19" s="9">
-        <v>15</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.5</v>
+        <v>20</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19357,7 +21604,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="9">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19373,8 +21620,8 @@
       <c r="D21" s="9">
         <v>20</v>
       </c>
-      <c r="E21" s="5">
-        <v>0.2</v>
+      <c r="E21" s="9">
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19390,8 +21637,8 @@
       <c r="D22" s="9">
         <v>20</v>
       </c>
-      <c r="E22" s="9">
-        <v>0.25</v>
+      <c r="E22" s="5">
+        <v>0.35</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19408,7 +21655,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19424,8 +21671,8 @@
       <c r="D24" s="9">
         <v>20</v>
       </c>
-      <c r="E24" s="5">
-        <v>0.35</v>
+      <c r="E24" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19441,8 +21688,8 @@
       <c r="D25" s="9">
         <v>20</v>
       </c>
-      <c r="E25" s="9">
-        <v>0.4</v>
+      <c r="E25" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19450,7 +21697,7 @@
         <v>79</v>
       </c>
       <c r="B26" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C26" s="9">
         <v>0.6</v>
@@ -19458,8 +21705,8 @@
       <c r="D26" s="9">
         <v>20</v>
       </c>
-      <c r="E26" s="9">
-        <v>0.45</v>
+      <c r="E26" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19467,7 +21714,7 @@
         <v>80</v>
       </c>
       <c r="B27" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="9">
         <v>0.6</v>
@@ -19476,7 +21723,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="5">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19489,11 +21736,11 @@
       <c r="C28" s="9">
         <v>0.6</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="5">
         <v>20</v>
       </c>
       <c r="E28" s="5">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19506,11 +21753,11 @@
       <c r="C29" s="9">
         <v>0.6</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="5">
         <v>20</v>
       </c>
       <c r="E29" s="5">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19518,7 +21765,7 @@
         <v>83</v>
       </c>
       <c r="B30" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C30" s="9">
         <v>0.6</v>
@@ -19527,7 +21774,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="5">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19535,7 +21782,7 @@
         <v>84</v>
       </c>
       <c r="B31" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C31" s="9">
         <v>0.6</v>
@@ -19544,7 +21791,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="5">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19561,7 +21808,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="5">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19578,7 +21825,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="5">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19595,7 +21842,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="5">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19603,16 +21850,16 @@
         <v>88</v>
       </c>
       <c r="B35" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C35" s="9">
         <v>0.6</v>
       </c>
       <c r="D35" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E35" s="5">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19620,16 +21867,16 @@
         <v>89</v>
       </c>
       <c r="B36" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C36" s="9">
         <v>0.6</v>
       </c>
       <c r="D36" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E36" s="5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19637,16 +21884,16 @@
         <v>90</v>
       </c>
       <c r="B37" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C37" s="9">
         <v>0.6</v>
       </c>
       <c r="D37" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E37" s="5">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19663,7 +21910,7 @@
         <v>30</v>
       </c>
       <c r="E38" s="5">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19680,7 +21927,7 @@
         <v>30</v>
       </c>
       <c r="E39" s="5">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19697,7 +21944,7 @@
         <v>30</v>
       </c>
       <c r="E40" s="5">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19714,7 +21961,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19731,7 +21978,7 @@
         <v>30</v>
       </c>
       <c r="E42" s="5">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19739,7 +21986,7 @@
         <v>96</v>
       </c>
       <c r="B43" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C43" s="9">
         <v>0.6</v>
@@ -19748,7 +21995,7 @@
         <v>30</v>
       </c>
       <c r="E43" s="5">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19756,7 +22003,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C44" s="9">
         <v>0.6</v>
@@ -19765,7 +22012,7 @@
         <v>30</v>
       </c>
       <c r="E44" s="5">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19773,7 +22020,7 @@
         <v>98</v>
       </c>
       <c r="B45" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C45" s="9">
         <v>0.6</v>
@@ -19782,7 +22029,7 @@
         <v>30</v>
       </c>
       <c r="E45" s="5">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19799,7 +22046,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="5">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19807,7 +22054,7 @@
         <v>100</v>
       </c>
       <c r="B47" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C47" s="9">
         <v>0.6</v>
@@ -19816,7 +22063,7 @@
         <v>30</v>
       </c>
       <c r="E47" s="5">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19824,7 +22071,7 @@
         <v>101</v>
       </c>
       <c r="B48" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C48" s="9">
         <v>0.6</v>
@@ -19833,7 +22080,7 @@
         <v>30</v>
       </c>
       <c r="E48" s="5">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19841,7 +22088,7 @@
         <v>102</v>
       </c>
       <c r="B49" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C49" s="9">
         <v>0.6</v>
@@ -19850,7 +22097,7 @@
         <v>30</v>
       </c>
       <c r="E49" s="5">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19858,7 +22105,7 @@
         <v>103</v>
       </c>
       <c r="B50" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C50" s="9">
         <v>0.6</v>
@@ -19867,7 +22114,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="5">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19875,13 +22122,13 @@
         <v>104</v>
       </c>
       <c r="B51" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C51" s="9">
         <v>0.6</v>
       </c>
       <c r="D51" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E51" s="5">
         <v>0.15</v>
@@ -19892,16 +22139,16 @@
         <v>329</v>
       </c>
       <c r="B52" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C52" s="9">
         <v>0.6</v>
       </c>
       <c r="D52" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E52" s="5">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19909,16 +22156,16 @@
         <v>330</v>
       </c>
       <c r="B53" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C53" s="9">
         <v>0.6</v>
       </c>
       <c r="D53" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E53" s="5">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19926,16 +22173,16 @@
         <v>331</v>
       </c>
       <c r="B54" s="9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C54" s="9">
         <v>0.6</v>
       </c>
       <c r="D54" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E54" s="5">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19952,7 +22199,7 @@
         <v>40</v>
       </c>
       <c r="E55" s="5">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19969,7 +22216,7 @@
         <v>40</v>
       </c>
       <c r="E56" s="5">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -19986,7 +22233,7 @@
         <v>40</v>
       </c>
       <c r="E57" s="5">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20003,7 +22250,7 @@
         <v>40</v>
       </c>
       <c r="E58" s="5">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20011,7 +22258,7 @@
         <v>336</v>
       </c>
       <c r="B59" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C59" s="9">
         <v>0.6</v>
@@ -20020,7 +22267,7 @@
         <v>40</v>
       </c>
       <c r="E59" s="5">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20028,7 +22275,7 @@
         <v>337</v>
       </c>
       <c r="B60" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C60" s="9">
         <v>0.6</v>
@@ -20037,7 +22284,7 @@
         <v>40</v>
       </c>
       <c r="E60" s="5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20045,7 +22292,7 @@
         <v>338</v>
       </c>
       <c r="B61" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C61" s="9">
         <v>0.6</v>
@@ -20054,7 +22301,7 @@
         <v>40</v>
       </c>
       <c r="E61" s="5">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20062,7 +22309,7 @@
         <v>339</v>
       </c>
       <c r="B62" s="9">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C62" s="9">
         <v>0.6</v>
@@ -20071,7 +22318,7 @@
         <v>40</v>
       </c>
       <c r="E62" s="5">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20079,7 +22326,7 @@
         <v>340</v>
       </c>
       <c r="B63" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C63" s="9">
         <v>0.6</v>
@@ -20088,7 +22335,7 @@
         <v>40</v>
       </c>
       <c r="E63" s="5">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20096,7 +22343,7 @@
         <v>341</v>
       </c>
       <c r="B64" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C64" s="9">
         <v>0.6</v>
@@ -20105,7 +22352,7 @@
         <v>40</v>
       </c>
       <c r="E64" s="5">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20113,7 +22360,7 @@
         <v>342</v>
       </c>
       <c r="B65" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C65" s="9">
         <v>0.6</v>
@@ -20130,7 +22377,7 @@
         <v>343</v>
       </c>
       <c r="B66" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C66" s="9">
         <v>0.6</v>
@@ -20139,7 +22386,7 @@
         <v>40</v>
       </c>
       <c r="E66" s="5">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -20147,7 +22394,7 @@
         <v>360</v>
       </c>
       <c r="B67" s="9">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C67" s="9">
         <v>0.6</v>
@@ -20156,126 +22403,7 @@
         <v>40</v>
       </c>
       <c r="E67" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="B68" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C68" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D68" s="5">
-        <v>40</v>
-      </c>
-      <c r="E68" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="B69" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C69" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D69" s="5">
-        <v>40</v>
-      </c>
-      <c r="E69" s="5">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B70" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C70" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D70" s="5">
-        <v>40</v>
-      </c>
-      <c r="E70" s="5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="B71" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C71" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D71" s="5">
-        <v>40</v>
-      </c>
-      <c r="E71" s="5">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="B72" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C72" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D72" s="5">
-        <v>40</v>
-      </c>
-      <c r="E72" s="5">
         <v>0.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="B73" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C73" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D73" s="5">
-        <v>40</v>
-      </c>
-      <c r="E73" s="5">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B74" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C74" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D74" s="5">
-        <v>40</v>
-      </c>
-      <c r="E74" s="5">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -20284,7 +22412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAEAADE4-1974-425B-9B60-7A622B00931B}">
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -21459,9 +23587,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0F3900-65F7-43B2-A1AE-0D74F16FB7D2}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" style="3" customWidth="1"/>
@@ -21495,7 +23623,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
@@ -21509,7 +23637,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
@@ -21523,389 +23651,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C5" s="5">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
         <v>412</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF015CF3-8BB9-454A-A6BB-C5321D3A23AD}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="11.1796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" style="3" customWidth="1"/>
-    <col min="4" max="5" width="21.6328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.7265625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.7265625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="18.08984375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.90625" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>50</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="E2" s="5">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5">
-        <v>40</v>
-      </c>
-      <c r="G2" s="5">
-        <v>25</v>
-      </c>
-      <c r="H2" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>50</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="E3" s="5">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5">
-        <v>40</v>
-      </c>
-      <c r="G3" s="5">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>50</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="E4" s="5">
-        <v>15</v>
-      </c>
-      <c r="F4" s="5">
-        <v>40</v>
-      </c>
-      <c r="G4" s="5">
-        <v>25</v>
-      </c>
-      <c r="H4" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="E5" s="5">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5">
-        <v>40</v>
-      </c>
-      <c r="G5" s="5">
-        <v>25</v>
-      </c>
-      <c r="H5" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <v>50</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="E6" s="5">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5">
-        <v>40</v>
-      </c>
-      <c r="G6" s="5">
-        <v>25</v>
-      </c>
-      <c r="H6" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>50</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="E7" s="5">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5">
-        <v>40</v>
-      </c>
-      <c r="G7" s="5">
-        <v>25</v>
-      </c>
-      <c r="H7" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>50</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.71</v>
-      </c>
-      <c r="E8" s="5">
-        <v>13</v>
-      </c>
-      <c r="F8" s="5">
-        <v>40</v>
-      </c>
-      <c r="G8" s="5">
-        <v>25</v>
-      </c>
-      <c r="H8" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <v>50</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="E9" s="5">
-        <v>14</v>
-      </c>
-      <c r="F9" s="5">
-        <v>40</v>
-      </c>
-      <c r="G9" s="5">
-        <v>25</v>
-      </c>
-      <c r="H9" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>50</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="E10" s="5">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5">
-        <v>40</v>
-      </c>
-      <c r="G10" s="5">
-        <v>25</v>
-      </c>
-      <c r="H10" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>50</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="E11" s="5">
-        <v>16</v>
-      </c>
-      <c r="F11" s="5">
-        <v>40</v>
-      </c>
-      <c r="G11" s="5">
-        <v>25</v>
-      </c>
-      <c r="H11" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <v>50</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.73</v>
-      </c>
-      <c r="E12" s="5">
-        <v>17</v>
-      </c>
-      <c r="F12" s="5">
-        <v>60</v>
-      </c>
-      <c r="G12" s="5">
-        <v>25</v>
-      </c>
-      <c r="H12" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <v>50</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="E13" s="5">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5">
-        <v>60</v>
-      </c>
-      <c r="G13" s="5">
-        <v>25</v>
-      </c>
-      <c r="H13" s="8">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Device_Config_Rings.xlsx
+++ b/Device_Config_Rings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abmai\Downloads\Aeluma_1\Aeluma_1_Ankit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA121769-E3D4-4045-83A4-396A771DA095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEEFFAB-F023-45E1-8899-822263B936EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhC_ADF_EC" sheetId="66" r:id="rId1"/>
@@ -3376,7 +3376,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3393,7 +3393,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="1">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3410,7 +3410,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3427,7 +3427,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3444,7 +3444,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3461,7 +3461,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3478,7 +3478,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3495,7 +3495,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3512,7 +3512,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3529,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3537,7 +3537,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="1">
         <v>0.6</v>
@@ -3546,7 +3546,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3554,7 +3554,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="1">
         <v>0.6</v>
@@ -3563,7 +3563,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="1">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3571,7 +3571,7 @@
         <v>28</v>
       </c>
       <c r="B14" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C14" s="1">
         <v>0.6</v>
@@ -3580,7 +3580,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="1">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3588,7 +3588,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="1">
         <v>0.6</v>
@@ -3597,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="1">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3605,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="B16" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C16" s="1">
         <v>0.6</v>
@@ -3614,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3622,7 +3622,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C17" s="1">
         <v>0.6</v>
@@ -3631,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="1">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3639,7 +3639,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C18" s="1">
         <v>0.6</v>
@@ -3648,7 +3648,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="1">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3665,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3682,7 +3682,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1">
-        <v>0.4</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3699,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3716,7 +3716,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="1">
-        <v>0.5</v>
+        <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3733,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="1">
-        <v>0.55000000000000004</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3750,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="E24" s="1">
-        <v>0.6</v>
+        <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3767,7 +3767,7 @@
         <v>15</v>
       </c>
       <c r="E25" s="1">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3784,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="E26" s="1">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3801,7 +3801,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7">
-        <v>0.55000000000000004</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3818,7 +3818,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3835,7 +3835,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3852,7 +3852,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="7">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3869,7 +3869,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="7">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3886,7 +3886,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="7">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3903,7 +3903,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="7">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3920,7 +3920,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="7">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3937,7 +3937,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="7">
-        <v>0.95</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3945,7 +3945,7 @@
         <v>53</v>
       </c>
       <c r="B36" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C36" s="1">
         <v>0.6</v>
@@ -3954,7 +3954,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="7">
-        <v>1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3988,7 +3988,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="7">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4005,7 +4005,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="7">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4022,7 +4022,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="7">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4039,7 +4039,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="7">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4056,7 +4056,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="7">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4064,7 +4064,7 @@
         <v>60</v>
       </c>
       <c r="B43" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C43" s="1">
         <v>0.6</v>
@@ -4073,7 +4073,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="7">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4081,7 +4081,7 @@
         <v>61</v>
       </c>
       <c r="B44" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C44" s="1">
         <v>0.6</v>
@@ -4090,7 +4090,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="7">
-        <v>0.45</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4098,7 +4098,7 @@
         <v>62</v>
       </c>
       <c r="B45" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C45" s="1">
         <v>0.6</v>
@@ -4107,7 +4107,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="7">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4115,7 +4115,7 @@
         <v>63</v>
       </c>
       <c r="B46" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C46" s="1">
         <v>0.6</v>
@@ -4124,7 +4124,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="7">
-        <v>0.55000000000000004</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4132,7 +4132,7 @@
         <v>64</v>
       </c>
       <c r="B47" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C47" s="1">
         <v>0.6</v>
@@ -4141,7 +4141,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="7">
-        <v>0.6</v>
+        <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4149,7 +4149,7 @@
         <v>65</v>
       </c>
       <c r="B48" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C48" s="1">
         <v>0.6</v>
@@ -4158,7 +4158,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="7">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4166,7 +4166,7 @@
         <v>66</v>
       </c>
       <c r="B49" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C49" s="1">
         <v>0.6</v>
@@ -4175,7 +4175,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="7">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4192,7 +4192,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="7">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4353,7 +4353,7 @@
         <v>353</v>
       </c>
       <c r="B60" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C60" s="1">
         <v>0.6</v>
@@ -4362,7 +4362,7 @@
         <v>30</v>
       </c>
       <c r="E60" s="7">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4370,7 +4370,7 @@
         <v>354</v>
       </c>
       <c r="B61" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C61" s="1">
         <v>0.6</v>
@@ -4379,7 +4379,7 @@
         <v>30</v>
       </c>
       <c r="E61" s="7">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4387,7 +4387,7 @@
         <v>355</v>
       </c>
       <c r="B62" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C62" s="1">
         <v>0.6</v>
@@ -4396,7 +4396,7 @@
         <v>30</v>
       </c>
       <c r="E62" s="7">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4404,7 +4404,7 @@
         <v>356</v>
       </c>
       <c r="B63" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C63" s="1">
         <v>0.6</v>
@@ -4413,7 +4413,7 @@
         <v>30</v>
       </c>
       <c r="E63" s="7">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4421,7 +4421,7 @@
         <v>357</v>
       </c>
       <c r="B64" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C64" s="1">
         <v>0.6</v>
@@ -4430,7 +4430,7 @@
         <v>30</v>
       </c>
       <c r="E64" s="7">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4438,7 +4438,7 @@
         <v>358</v>
       </c>
       <c r="B65" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C65" s="1">
         <v>0.6</v>
@@ -4447,7 +4447,7 @@
         <v>30</v>
       </c>
       <c r="E65" s="7">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4455,7 +4455,7 @@
         <v>359</v>
       </c>
       <c r="B66" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C66" s="9">
         <v>0.6</v>
@@ -4464,7 +4464,7 @@
         <v>30</v>
       </c>
       <c r="E66" s="5">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4472,7 +4472,7 @@
         <v>384</v>
       </c>
       <c r="B67" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C67" s="9">
         <v>0.6</v>
@@ -4481,7 +4481,7 @@
         <v>30</v>
       </c>
       <c r="E67" s="5">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4489,7 +4489,7 @@
         <v>385</v>
       </c>
       <c r="B68" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C68" s="9">
         <v>0.6</v>
@@ -4498,7 +4498,7 @@
         <v>30</v>
       </c>
       <c r="E68" s="5">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4506,7 +4506,7 @@
         <v>386</v>
       </c>
       <c r="B69" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C69" s="9">
         <v>0.6</v>
@@ -4515,7 +4515,7 @@
         <v>30</v>
       </c>
       <c r="E69" s="5">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4532,7 +4532,7 @@
         <v>40</v>
       </c>
       <c r="E70" s="5">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4676,7 +4676,7 @@
         <v>396</v>
       </c>
       <c r="B79" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C79" s="9">
         <v>0.6</v>
@@ -4685,7 +4685,7 @@
         <v>40</v>
       </c>
       <c r="E79" s="5">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4693,7 +4693,7 @@
         <v>397</v>
       </c>
       <c r="B80" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C80" s="9">
         <v>0.6</v>
@@ -4702,7 +4702,7 @@
         <v>40</v>
       </c>
       <c r="E80" s="5">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4710,7 +4710,7 @@
         <v>398</v>
       </c>
       <c r="B81" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C81" s="9">
         <v>0.6</v>
@@ -4719,7 +4719,7 @@
         <v>40</v>
       </c>
       <c r="E81" s="5">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4727,7 +4727,7 @@
         <v>399</v>
       </c>
       <c r="B82" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C82" s="9">
         <v>0.6</v>
@@ -4736,7 +4736,7 @@
         <v>40</v>
       </c>
       <c r="E82" s="5">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4744,7 +4744,7 @@
         <v>400</v>
       </c>
       <c r="B83" s="5">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C83" s="9">
         <v>0.6</v>
@@ -4753,7 +4753,7 @@
         <v>40</v>
       </c>
       <c r="E83" s="5">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4761,7 +4761,7 @@
         <v>401</v>
       </c>
       <c r="B84" s="5">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C84" s="9">
         <v>0.6</v>
@@ -4770,7 +4770,7 @@
         <v>40</v>
       </c>
       <c r="E84" s="5">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4778,7 +4778,7 @@
         <v>402</v>
       </c>
       <c r="B85" s="5">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C85" s="9">
         <v>0.6</v>
@@ -4787,7 +4787,7 @@
         <v>40</v>
       </c>
       <c r="E85" s="5">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4795,7 +4795,7 @@
         <v>403</v>
       </c>
       <c r="B86" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C86" s="9">
         <v>0.6</v>
@@ -4804,7 +4804,7 @@
         <v>40</v>
       </c>
       <c r="E86" s="5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4812,7 +4812,7 @@
         <v>404</v>
       </c>
       <c r="B87" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C87" s="9">
         <v>0.6</v>
@@ -4821,7 +4821,7 @@
         <v>40</v>
       </c>
       <c r="E87" s="5">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -4881,11 +4881,11 @@
         <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
         <f>E2/D2*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G2" s="1">
         <v>0.2</v>
@@ -4905,14 +4905,14 @@
         <v>15</v>
       </c>
       <c r="E3" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" ref="F3:F12" si="0">E3/D3*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G3" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4929,14 +4929,14 @@
         <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G4" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4953,14 +4953,14 @@
         <v>15</v>
       </c>
       <c r="E5" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G5" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4977,14 +4977,14 @@
         <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G6" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5001,14 +5001,14 @@
         <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G7" s="1">
-        <v>0.32500000000000001</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5025,14 +5025,14 @@
         <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G8" s="1">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5049,14 +5049,14 @@
         <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G9" s="1">
-        <v>0.375</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5073,14 +5073,14 @@
         <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G10" s="1">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5097,14 +5097,14 @@
         <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G11" s="1">
-        <v>0.42499999999999999</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5121,14 +5121,14 @@
         <v>15</v>
       </c>
       <c r="E12" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="0"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G12" s="1">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5136,7 +5136,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="1">
         <v>0.6</v>
@@ -5145,14 +5145,14 @@
         <v>15</v>
       </c>
       <c r="E13" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1">
         <f>E13/D13*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G13" s="1">
-        <v>0.47499999999999998</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5160,7 +5160,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C14" s="1">
         <v>0.6</v>
@@ -5169,14 +5169,14 @@
         <v>15</v>
       </c>
       <c r="E14" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ref="F14:F16" si="1">E14/D14*180/PI()</f>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G14" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5184,7 +5184,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="1">
         <v>0.6</v>
@@ -5193,14 +5193,14 @@
         <v>15</v>
       </c>
       <c r="E15" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="1"/>
-        <v>22.918311805232928</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G15" s="1">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5208,7 +5208,7 @@
         <v>69</v>
       </c>
       <c r="B16" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C16" s="1">
         <v>0.6</v>
@@ -5217,14 +5217,14 @@
         <v>15</v>
       </c>
       <c r="E16" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="1"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G16" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5232,7 +5232,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C17" s="1">
         <v>0.6</v>
@@ -5241,14 +5241,14 @@
         <v>15</v>
       </c>
       <c r="E17" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" ref="F17:F27" si="2">E17/D17*180/PI()</f>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5256,7 +5256,7 @@
         <v>71</v>
       </c>
       <c r="B18" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C18" s="1">
         <v>0.6</v>
@@ -5265,14 +5265,14 @@
         <v>15</v>
       </c>
       <c r="E18" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G18" s="1">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5280,7 +5280,7 @@
         <v>72</v>
       </c>
       <c r="B19" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C19" s="1">
         <v>0.6</v>
@@ -5289,14 +5289,14 @@
         <v>15</v>
       </c>
       <c r="E19" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>7.6394372684109761</v>
       </c>
       <c r="G19" s="1">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5304,7 +5304,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C20" s="1">
         <v>0.6</v>
@@ -5313,14 +5313,14 @@
         <v>15</v>
       </c>
       <c r="E20" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G20" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5328,7 +5328,7 @@
         <v>74</v>
       </c>
       <c r="B21" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C21" s="1">
         <v>0.6</v>
@@ -5337,14 +5337,14 @@
         <v>15</v>
       </c>
       <c r="E21" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>22.918311805232928</v>
       </c>
       <c r="G21" s="1">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5352,7 +5352,7 @@
         <v>75</v>
       </c>
       <c r="B22" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C22" s="1">
         <v>0.6</v>
@@ -5368,7 +5368,7 @@
         <v>30.557749073643905</v>
       </c>
       <c r="G22" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5385,14 +5385,14 @@
         <v>15</v>
       </c>
       <c r="E23" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G23" s="1">
-        <v>0.55000000000000004</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5409,14 +5409,14 @@
         <v>15</v>
       </c>
       <c r="E24" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G24" s="1">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5433,14 +5433,14 @@
         <v>15</v>
       </c>
       <c r="E25" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G25" s="1">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5457,14 +5457,14 @@
         <v>15</v>
       </c>
       <c r="E26" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G26" s="1">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5481,14 +5481,14 @@
         <v>15</v>
       </c>
       <c r="E27" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" si="2"/>
-        <v>30.557749073643905</v>
+        <v>15.278874536821952</v>
       </c>
       <c r="G27" s="1">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -12717,7 +12717,7 @@
     <col min="2" max="2" width="14.453125" style="6" customWidth="1"/>
     <col min="3" max="3" width="18.7265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.7265625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.1796875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.1796875" style="5" customWidth="1"/>
     <col min="6" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
@@ -12725,16 +12725,16 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -12742,1207 +12742,1207 @@
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="9">
         <v>0.6</v>
       </c>
       <c r="C2" s="1">
         <v>0.6</v>
       </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.1</v>
+      <c r="D2" s="9">
+        <v>15</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="9">
         <v>0.6</v>
       </c>
       <c r="C3" s="1">
         <v>0.6</v>
       </c>
-      <c r="D3" s="1">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.15</v>
+      <c r="D3" s="9">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="9">
         <v>0.6</v>
       </c>
       <c r="C4" s="1">
         <v>0.6</v>
       </c>
-      <c r="D4" s="1">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.2</v>
+      <c r="D4" s="9">
+        <v>15</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="9">
         <v>0.6</v>
       </c>
       <c r="C5" s="1">
         <v>0.6</v>
       </c>
-      <c r="D5" s="1">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.25</v>
+      <c r="D5" s="9">
+        <v>15</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="9">
         <v>0.6</v>
       </c>
       <c r="C6" s="1">
         <v>0.6</v>
       </c>
-      <c r="D6" s="1">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.3</v>
+      <c r="D6" s="9">
+        <v>15</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="9">
         <v>0.6</v>
       </c>
       <c r="C7" s="1">
         <v>0.6</v>
       </c>
-      <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.35</v>
+      <c r="D7" s="9">
+        <v>15</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="9">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
         <v>0.6</v>
       </c>
-      <c r="D8" s="1">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.4</v>
+      <c r="D8" s="9">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="9">
         <v>0.6</v>
       </c>
       <c r="C9" s="1">
         <v>0.6</v>
       </c>
-      <c r="D9" s="1">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.45</v>
+      <c r="D9" s="9">
+        <v>15</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="9">
         <v>0.6</v>
       </c>
       <c r="C10" s="1">
         <v>0.6</v>
       </c>
-      <c r="D10" s="1">
-        <v>15</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.5</v>
+      <c r="D10" s="9">
+        <v>15</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="9">
         <v>0.7</v>
       </c>
       <c r="C11" s="1">
         <v>0.6</v>
       </c>
-      <c r="D11" s="1">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.1</v>
+      <c r="D11" s="9">
+        <v>15</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="9">
         <v>0.7</v>
       </c>
       <c r="C12" s="1">
         <v>0.6</v>
       </c>
-      <c r="D12" s="1">
-        <v>15</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.15</v>
+      <c r="D12" s="9">
+        <v>15</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>0.7</v>
       </c>
       <c r="C13" s="1">
         <v>0.6</v>
       </c>
-      <c r="D13" s="1">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.2</v>
+      <c r="D13" s="9">
+        <v>15</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>0.7</v>
       </c>
       <c r="C14" s="1">
         <v>0.6</v>
       </c>
-      <c r="D14" s="1">
-        <v>15</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.25</v>
+      <c r="D14" s="9">
+        <v>15</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <v>0.7</v>
       </c>
       <c r="C15" s="1">
         <v>0.6</v>
       </c>
-      <c r="D15" s="1">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.3</v>
+      <c r="D15" s="9">
+        <v>15</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.35</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="9">
         <v>0.7</v>
       </c>
       <c r="C16" s="1">
         <v>0.6</v>
       </c>
-      <c r="D16" s="1">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.35</v>
+      <c r="D16" s="9">
+        <v>15</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="9">
         <v>0.7</v>
       </c>
       <c r="C17" s="1">
         <v>0.6</v>
       </c>
-      <c r="D17" s="1">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.4</v>
+      <c r="D17" s="9">
+        <v>15</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="1">
-        <v>0.8</v>
+      <c r="B18" s="9">
+        <v>0.7</v>
       </c>
       <c r="C18" s="1">
         <v>0.6</v>
       </c>
-      <c r="D18" s="1">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.1</v>
+      <c r="D18" s="9">
+        <v>15</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="1">
-        <v>0.8</v>
+      <c r="B19" s="9">
+        <v>0.7</v>
       </c>
       <c r="C19" s="1">
         <v>0.6</v>
       </c>
-      <c r="D19" s="1">
-        <v>15</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.15</v>
+      <c r="D19" s="9">
+        <v>15</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="9">
         <v>0.8</v>
       </c>
       <c r="C20" s="1">
         <v>0.6</v>
       </c>
-      <c r="D20" s="1">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.2</v>
+      <c r="D20" s="9">
+        <v>15</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="9">
         <v>0.8</v>
       </c>
       <c r="C21" s="1">
         <v>0.6</v>
       </c>
-      <c r="D21" s="1">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0.25</v>
+      <c r="D21" s="9">
+        <v>15</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="9">
         <v>0.8</v>
       </c>
       <c r="C22" s="1">
         <v>0.6</v>
       </c>
-      <c r="D22" s="1">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.3</v>
+      <c r="D22" s="9">
+        <v>15</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="9">
         <v>0.8</v>
       </c>
       <c r="C23" s="1">
         <v>0.6</v>
       </c>
-      <c r="D23" s="1">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.35</v>
+      <c r="D23" s="9">
+        <v>15</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="9">
         <v>0.8</v>
       </c>
       <c r="C24" s="1">
         <v>0.6</v>
       </c>
-      <c r="D24" s="1">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.4</v>
+      <c r="D24" s="9">
+        <v>15</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="9">
         <v>0.8</v>
       </c>
       <c r="C25" s="1">
         <v>0.6</v>
       </c>
-      <c r="D25" s="1">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.45</v>
+      <c r="D25" s="9">
+        <v>15</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="9">
         <v>0.8</v>
       </c>
       <c r="C26" s="1">
         <v>0.6</v>
       </c>
-      <c r="D26" s="1">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.5</v>
+      <c r="D26" s="9">
+        <v>15</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.35</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="9">
         <v>0.8</v>
       </c>
       <c r="C27" s="1">
         <v>0.6</v>
       </c>
-      <c r="D27" s="1">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.17499999999999999</v>
+      <c r="D27" s="9">
+        <v>15</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="9">
         <v>0.6</v>
       </c>
       <c r="C28" s="1">
         <v>0.6</v>
       </c>
-      <c r="D28" s="1">
-        <v>20</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.1</v>
+      <c r="D28" s="9">
+        <v>20</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="9">
         <v>0.6</v>
       </c>
       <c r="C29" s="1">
         <v>0.6</v>
       </c>
-      <c r="D29" s="1">
-        <v>20</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.125</v>
+      <c r="D29" s="9">
+        <v>20</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="9">
         <v>0.6</v>
       </c>
       <c r="C30" s="1">
         <v>0.6</v>
       </c>
-      <c r="D30" s="1">
-        <v>20</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.15</v>
+      <c r="D30" s="9">
+        <v>20</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="9">
         <v>0.6</v>
       </c>
       <c r="C31" s="1">
         <v>0.6</v>
       </c>
-      <c r="D31" s="1">
-        <v>20</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.17499999999999999</v>
+      <c r="D31" s="9">
+        <v>20</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="9">
         <v>0.6</v>
       </c>
       <c r="C32" s="1">
         <v>0.6</v>
       </c>
-      <c r="D32" s="1">
-        <v>20</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.2</v>
+      <c r="D32" s="9">
+        <v>20</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.35</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="9">
         <v>0.6</v>
       </c>
       <c r="C33" s="1">
         <v>0.6</v>
       </c>
-      <c r="D33" s="1">
-        <v>20</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.22500000000000001</v>
+      <c r="D33" s="9">
+        <v>20</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="9">
         <v>0.6</v>
       </c>
       <c r="C34" s="1">
         <v>0.6</v>
       </c>
-      <c r="D34" s="1">
-        <v>20</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.25</v>
+      <c r="D34" s="9">
+        <v>20</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0.45</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="9">
         <v>0.6</v>
       </c>
       <c r="C35" s="1">
         <v>0.6</v>
       </c>
-      <c r="D35" s="1">
-        <v>20</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.27500000000000002</v>
+      <c r="D35" s="9">
+        <v>20</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="9">
         <v>0.6</v>
       </c>
       <c r="C36" s="1">
         <v>0.6</v>
       </c>
-      <c r="D36" s="1">
-        <v>20</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.3</v>
+      <c r="D36" s="9">
+        <v>20</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="9">
         <v>0.6</v>
       </c>
       <c r="C37" s="1">
         <v>0.6</v>
       </c>
-      <c r="D37" s="1">
-        <v>20</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.32500000000000001</v>
+      <c r="D37" s="9">
+        <v>20</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.6</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="1">
-        <v>0.6</v>
+      <c r="B38" s="9">
+        <v>0.7</v>
       </c>
       <c r="C38" s="1">
         <v>0.6</v>
       </c>
-      <c r="D38" s="1">
-        <v>20</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.35</v>
+      <c r="D38" s="9">
+        <v>20</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="1">
-        <v>0.6</v>
+      <c r="B39" s="9">
+        <v>0.7</v>
       </c>
       <c r="C39" s="1">
         <v>0.6</v>
       </c>
-      <c r="D39" s="1">
-        <v>20</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.375</v>
+      <c r="D39" s="9">
+        <v>20</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="1">
-        <v>0.6</v>
+      <c r="B40" s="9">
+        <v>0.7</v>
       </c>
       <c r="C40" s="1">
         <v>0.6</v>
       </c>
-      <c r="D40" s="1">
-        <v>20</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.4</v>
+      <c r="D40" s="9">
+        <v>20</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="1">
-        <v>0.6</v>
+      <c r="B41" s="9">
+        <v>0.7</v>
       </c>
       <c r="C41" s="1">
         <v>0.6</v>
       </c>
-      <c r="D41" s="1">
-        <v>20</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.42499999999999999</v>
+      <c r="D41" s="9">
+        <v>20</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.3</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="1">
-        <v>0.6</v>
+      <c r="B42" s="9">
+        <v>0.7</v>
       </c>
       <c r="C42" s="1">
         <v>0.6</v>
       </c>
-      <c r="D42" s="1">
-        <v>20</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.45</v>
+      <c r="D42" s="9">
+        <v>20</v>
+      </c>
+      <c r="E42" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="1">
-        <v>0.6</v>
+      <c r="B43" s="9">
+        <v>0.7</v>
       </c>
       <c r="C43" s="1">
         <v>0.6</v>
       </c>
-      <c r="D43" s="1">
-        <v>20</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.47499999999999998</v>
+      <c r="D43" s="9">
+        <v>20</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="1">
-        <v>0.6</v>
+      <c r="B44" s="9">
+        <v>0.7</v>
       </c>
       <c r="C44" s="1">
         <v>0.6</v>
       </c>
-      <c r="D44" s="1">
-        <v>20</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.5</v>
+      <c r="D44" s="9">
+        <v>20</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.6</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="1">
-        <v>0.7</v>
+      <c r="B45" s="9">
+        <v>0.8</v>
       </c>
       <c r="C45" s="1">
         <v>0.6</v>
       </c>
-      <c r="D45" s="1">
-        <v>20</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.1</v>
+      <c r="D45" s="9">
+        <v>20</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="1">
-        <v>0.7</v>
+      <c r="B46" s="9">
+        <v>0.8</v>
       </c>
       <c r="C46" s="1">
         <v>0.6</v>
       </c>
-      <c r="D46" s="1">
-        <v>20</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.15</v>
+      <c r="D46" s="9">
+        <v>20</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="1">
-        <v>0.7</v>
+      <c r="B47" s="9">
+        <v>0.8</v>
       </c>
       <c r="C47" s="1">
         <v>0.6</v>
       </c>
-      <c r="D47" s="1">
-        <v>20</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.2</v>
+      <c r="D47" s="9">
+        <v>20</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B48" s="1">
-        <v>0.7</v>
+      <c r="B48" s="9">
+        <v>0.8</v>
       </c>
       <c r="C48" s="1">
         <v>0.6</v>
       </c>
-      <c r="D48" s="1">
-        <v>20</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.25</v>
+      <c r="D48" s="9">
+        <v>20</v>
+      </c>
+      <c r="E48" s="5">
+        <v>0.3</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="1">
-        <v>0.7</v>
+      <c r="B49" s="9">
+        <v>0.8</v>
       </c>
       <c r="C49" s="1">
         <v>0.6</v>
       </c>
-      <c r="D49" s="1">
-        <v>20</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.3</v>
+      <c r="D49" s="9">
+        <v>20</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0.35</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="1">
-        <v>0.7</v>
+      <c r="B50" s="9">
+        <v>0.8</v>
       </c>
       <c r="C50" s="1">
         <v>0.6</v>
       </c>
-      <c r="D50" s="1">
-        <v>20</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.35</v>
+      <c r="D50" s="9">
+        <v>20</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="1">
-        <v>0.7</v>
+      <c r="B51" s="9">
+        <v>0.8</v>
       </c>
       <c r="C51" s="1">
         <v>0.6</v>
       </c>
-      <c r="D51" s="1">
-        <v>20</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.4</v>
+      <c r="D51" s="9">
+        <v>20</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.45</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="9">
         <v>0.6</v>
       </c>
       <c r="C52" s="1">
         <v>0.6</v>
       </c>
-      <c r="D52" s="1">
-        <v>30</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.1</v>
+      <c r="D52" s="9">
+        <v>30</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="9">
         <v>0.6</v>
       </c>
       <c r="C53" s="1">
         <v>0.6</v>
       </c>
-      <c r="D53" s="1">
-        <v>30</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.15</v>
+      <c r="D53" s="9">
+        <v>30</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="9">
         <v>0.6</v>
       </c>
       <c r="C54" s="1">
         <v>0.6</v>
       </c>
-      <c r="D54" s="1">
-        <v>30</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.2</v>
+      <c r="D54" s="9">
+        <v>30</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="9">
         <v>0.6</v>
       </c>
       <c r="C55" s="1">
         <v>0.6</v>
       </c>
-      <c r="D55" s="1">
-        <v>30</v>
-      </c>
-      <c r="E55" s="7">
-        <v>0.25</v>
+      <c r="D55" s="9">
+        <v>30</v>
+      </c>
+      <c r="E55" s="5">
+        <v>0.3</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="9">
         <v>0.6</v>
       </c>
       <c r="C56" s="1">
         <v>0.6</v>
       </c>
-      <c r="D56" s="1">
-        <v>30</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.3</v>
+      <c r="D56" s="9">
+        <v>30</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0.35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="9">
         <v>0.6</v>
       </c>
       <c r="C57" s="1">
         <v>0.6</v>
       </c>
-      <c r="D57" s="1">
-        <v>30</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.35</v>
+      <c r="D57" s="9">
+        <v>30</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="9">
         <v>0.6</v>
       </c>
       <c r="C58" s="1">
         <v>0.6</v>
       </c>
-      <c r="D58" s="1">
-        <v>30</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.4</v>
+      <c r="D58" s="9">
+        <v>30</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.45</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="9">
         <v>0.6</v>
       </c>
       <c r="C59" s="1">
         <v>0.6</v>
       </c>
-      <c r="D59" s="1">
-        <v>30</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.45</v>
+      <c r="D59" s="9">
+        <v>30</v>
+      </c>
+      <c r="E59" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="9">
         <v>0.6</v>
       </c>
       <c r="C60" s="1">
         <v>0.6</v>
       </c>
-      <c r="D60" s="1">
-        <v>30</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.5</v>
+      <c r="D60" s="9">
+        <v>30</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B61" s="1">
-        <v>0.6</v>
+      <c r="B61" s="9">
+        <v>0.7</v>
       </c>
       <c r="C61" s="1">
         <v>0.6</v>
       </c>
-      <c r="D61" s="1">
-        <v>30</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.1</v>
+      <c r="D61" s="9">
+        <v>30</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B62" s="1">
-        <v>0.6</v>
+      <c r="B62" s="9">
+        <v>0.7</v>
       </c>
       <c r="C62" s="1">
         <v>0.6</v>
       </c>
-      <c r="D62" s="1">
-        <v>30</v>
-      </c>
-      <c r="E62" s="7">
-        <v>0.15</v>
+      <c r="D62" s="9">
+        <v>30</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B63" s="1">
-        <v>0.6</v>
+      <c r="B63" s="9">
+        <v>0.7</v>
       </c>
       <c r="C63" s="1">
         <v>0.6</v>
       </c>
-      <c r="D63" s="1">
-        <v>30</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.2</v>
+      <c r="D63" s="9">
+        <v>30</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.3</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="1">
-        <v>0.6</v>
+      <c r="B64" s="9">
+        <v>0.7</v>
       </c>
       <c r="C64" s="1">
         <v>0.6</v>
       </c>
-      <c r="D64" s="1">
-        <v>30</v>
-      </c>
-      <c r="E64" s="7">
-        <v>0.25</v>
+      <c r="D64" s="9">
+        <v>30</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B65" s="1">
-        <v>0.6</v>
+      <c r="B65" s="9">
+        <v>0.7</v>
       </c>
       <c r="C65" s="1">
         <v>0.6</v>
       </c>
-      <c r="D65" s="1">
-        <v>30</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.3</v>
+      <c r="D65" s="9">
+        <v>30</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B66" s="1">
-        <v>0.6</v>
+      <c r="B66" s="9">
+        <v>0.8</v>
       </c>
       <c r="C66" s="1">
         <v>0.6</v>
       </c>
-      <c r="D66" s="1">
-        <v>30</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.35</v>
+      <c r="D66" s="9">
+        <v>30</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.15</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B67" s="1">
-        <v>0.6</v>
+      <c r="B67" s="9">
+        <v>0.8</v>
       </c>
       <c r="C67" s="1">
         <v>0.6</v>
       </c>
-      <c r="D67" s="1">
-        <v>30</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.4</v>
+      <c r="D67" s="9">
+        <v>30</v>
+      </c>
+      <c r="E67" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B68" s="5">
-        <v>0.7</v>
+      <c r="B68" s="9">
+        <v>0.8</v>
       </c>
       <c r="C68" s="9">
         <v>0.6</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="9">
         <v>30</v>
       </c>
       <c r="E68" s="5">
-        <v>0.1</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B69" s="5">
-        <v>0.7</v>
+      <c r="B69" s="9">
+        <v>0.8</v>
       </c>
       <c r="C69" s="9">
         <v>0.6</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="9">
         <v>30</v>
       </c>
       <c r="E69" s="5">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B70" s="5">
-        <v>0.7</v>
+      <c r="B70" s="9">
+        <v>0.8</v>
       </c>
       <c r="C70" s="9">
         <v>0.6</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="9">
         <v>30</v>
       </c>
       <c r="E70" s="5">
-        <v>0.2</v>
+        <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B71" s="5">
-        <v>0.7</v>
+      <c r="B71" s="9">
+        <v>0.8</v>
       </c>
       <c r="C71" s="9">
         <v>0.6</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="9">
         <v>30</v>
       </c>
       <c r="E71" s="5">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B72" s="5">
-        <v>0.7</v>
+      <c r="B72" s="9">
+        <v>0.8</v>
       </c>
       <c r="C72" s="9">
         <v>0.6</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="9">
         <v>30</v>
       </c>
       <c r="E72" s="5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13950,7 +13950,7 @@
         <v>366</v>
       </c>
       <c r="B73" s="5">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C73" s="9">
         <v>0.6</v>
@@ -13959,7 +13959,7 @@
         <v>40</v>
       </c>
       <c r="E73" s="5">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13967,7 +13967,7 @@
         <v>367</v>
       </c>
       <c r="B74" s="5">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C74" s="9">
         <v>0.6</v>
@@ -13976,7 +13976,7 @@
         <v>40</v>
       </c>
       <c r="E74" s="5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -13984,7 +13984,7 @@
         <v>368</v>
       </c>
       <c r="B75" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C75" s="9">
         <v>0.6</v>
@@ -13993,7 +13993,7 @@
         <v>40</v>
       </c>
       <c r="E75" s="5">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14001,7 +14001,7 @@
         <v>369</v>
       </c>
       <c r="B76" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C76" s="9">
         <v>0.6</v>
@@ -14010,7 +14010,7 @@
         <v>40</v>
       </c>
       <c r="E76" s="5">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14018,7 +14018,7 @@
         <v>370</v>
       </c>
       <c r="B77" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C77" s="9">
         <v>0.6</v>
@@ -14027,7 +14027,7 @@
         <v>40</v>
       </c>
       <c r="E77" s="5">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14035,7 +14035,7 @@
         <v>371</v>
       </c>
       <c r="B78" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C78" s="9">
         <v>0.6</v>
@@ -14044,7 +14044,7 @@
         <v>40</v>
       </c>
       <c r="E78" s="5">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14052,7 +14052,7 @@
         <v>372</v>
       </c>
       <c r="B79" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C79" s="9">
         <v>0.6</v>
@@ -14061,7 +14061,7 @@
         <v>40</v>
       </c>
       <c r="E79" s="5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14069,7 +14069,7 @@
         <v>373</v>
       </c>
       <c r="B80" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C80" s="9">
         <v>0.6</v>
@@ -14078,7 +14078,7 @@
         <v>40</v>
       </c>
       <c r="E80" s="5">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14086,7 +14086,7 @@
         <v>374</v>
       </c>
       <c r="B81" s="5">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C81" s="9">
         <v>0.6</v>
@@ -14095,7 +14095,7 @@
         <v>40</v>
       </c>
       <c r="E81" s="5">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14103,7 +14103,7 @@
         <v>375</v>
       </c>
       <c r="B82" s="5">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="C82" s="9">
         <v>0.6</v>
@@ -14112,7 +14112,7 @@
         <v>40</v>
       </c>
       <c r="E82" s="5">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14120,7 +14120,7 @@
         <v>376</v>
       </c>
       <c r="B83" s="5">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="C83" s="9">
         <v>0.6</v>
@@ -14129,7 +14129,7 @@
         <v>40</v>
       </c>
       <c r="E83" s="5">
-        <v>0.125</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14137,7 +14137,7 @@
         <v>377</v>
       </c>
       <c r="B84" s="5">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="C84" s="9">
         <v>0.6</v>
@@ -14146,7 +14146,7 @@
         <v>40</v>
       </c>
       <c r="E84" s="5">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14154,7 +14154,7 @@
         <v>378</v>
       </c>
       <c r="B85" s="5">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="C85" s="9">
         <v>0.6</v>
@@ -14163,7 +14163,7 @@
         <v>40</v>
       </c>
       <c r="E85" s="5">
-        <v>0.17499999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14171,7 +14171,7 @@
         <v>379</v>
       </c>
       <c r="B86" s="5">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C86" s="9">
         <v>0.6</v>
@@ -14180,7 +14180,7 @@
         <v>40</v>
       </c>
       <c r="E86" s="5">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14188,7 +14188,7 @@
         <v>380</v>
       </c>
       <c r="B87" s="5">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C87" s="9">
         <v>0.6</v>
@@ -14197,7 +14197,7 @@
         <v>40</v>
       </c>
       <c r="E87" s="5">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -14205,7 +14205,7 @@
         <v>381</v>
       </c>
       <c r="B88" s="5">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C88" s="9">
         <v>0.6</v>
@@ -14222,7 +14222,7 @@
         <v>382</v>
       </c>
       <c r="B89" s="5">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C89" s="9">
         <v>0.6</v>
@@ -14239,7 +14239,7 @@
         <v>383</v>
       </c>
       <c r="B90" s="5">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C90" s="9">
         <v>0.6</v>
